--- a/data/trans_camb/P1403-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1403-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,09</t>
+          <t>9,98</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,41</t>
+          <t>6,65</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 10,06</t>
+          <t>0,56; 9,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 7,24</t>
+          <t>-2,05; 6,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 14,62</t>
+          <t>5,49; 14,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 4,16</t>
+          <t>-5,37; 5,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,99</t>
+          <t>-6,16; 4,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 6,27</t>
+          <t>-1,44; 7,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 6,14</t>
+          <t>-1,08; 5,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 4,2</t>
+          <t>-2,29; 4,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 9,35</t>
+          <t>3,25; 9,53</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>63,24%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 108,01</t>
+          <t>3,17; 103,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 81,82</t>
+          <t>-15,67; 75,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,83; 167,07</t>
+          <t>40,6; 176,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-47,12; 54,6</t>
+          <t>-42,88; 75,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 53,33</t>
+          <t>-49,62; 59,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 86,72</t>
+          <t>-11,64; 95,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 66,51</t>
+          <t>-8,47; 67,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 46,07</t>
+          <t>-18,82; 49,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,94; 108,26</t>
+          <t>23,98; 106,86</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,23</t>
+          <t>9,47</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,4</t>
+          <t>8,28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,69</t>
+          <t>9,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 5,59</t>
+          <t>-4,21; 5,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 8,07</t>
+          <t>-1,99; 7,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 13,8</t>
+          <t>4,47; 14,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 8,99</t>
+          <t>-0,22; 8,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 6,85</t>
+          <t>-0,74; 7,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 10,63</t>
+          <t>4,65; 11,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,95</t>
+          <t>-0,33; 5,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 6,3</t>
+          <t>-0,24; 6,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 11,64</t>
+          <t>6,0; 12,14</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>135,25%</t>
+          <t>151,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>99,99%</t>
+          <t>105,34%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 56,7</t>
+          <t>-29,05; 51,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 83,38</t>
+          <t>-14,66; 81,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,42; 147,79</t>
+          <t>30,29; 155,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 221,57</t>
+          <t>-4,35; 210,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 186,37</t>
+          <t>-16,48; 189,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,36; 292,95</t>
+          <t>55,94; 323,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 81,72</t>
+          <t>-6,28; 75,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,01; 87,96</t>
+          <t>-3,09; 83,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,1; 167,68</t>
+          <t>59,11; 167,83</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>7,76</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,73</t>
+          <t>11,46</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,58</t>
+          <t>8,79</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 13,3</t>
+          <t>4,0; 12,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 7,13</t>
+          <t>-1,21; 7,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 9,95</t>
+          <t>3,47; 12,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 16,59</t>
+          <t>2,55; 16,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 17,62</t>
+          <t>-0,3; 16,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 18,65</t>
+          <t>3,27; 17,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 12,59</t>
+          <t>5,04; 12,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 8,05</t>
+          <t>0,51; 8,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 10,05</t>
+          <t>5,29; 12,33</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,05; 120,78</t>
+          <t>25,16; 115,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 63,95</t>
+          <t>-7,73; 64,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-63,46; 80,39</t>
+          <t>22,24; 110,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,59; 184,37</t>
+          <t>13,03; 171,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 183,03</t>
+          <t>-2,34; 175,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,35; 214,92</t>
+          <t>15,71; 200,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,94; 114,42</t>
+          <t>33,26; 110,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 69,66</t>
+          <t>3,27; 75,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-56,86; 80,82</t>
+          <t>35,12; 104,61</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,17</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,18</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>2,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 5,62</t>
+          <t>-1,48; 5,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,36</t>
+          <t>-1,7; 4,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,46</t>
+          <t>0,73; 7,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 0,06</t>
+          <t>-6,72; 0,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 0,31</t>
+          <t>-6,17; 0,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 52,31</t>
+          <t>-2,07; 4,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,19</t>
+          <t>-2,53; 1,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1,78</t>
+          <t>-2,78; 1,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 32,54</t>
+          <t>0,36; 4,78</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>134,5%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 36,06</t>
+          <t>-8,13; 31,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 28,22</t>
+          <t>-8,98; 30,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,44; 48,22</t>
+          <t>3,58; 46,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 1,19</t>
+          <t>-42,42; 0,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 2,38</t>
+          <t>-38,82; 3,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 401,72</t>
+          <t>-12,69; 34,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 14,24</t>
+          <t>-14,89; 13,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 12,17</t>
+          <t>-16,48; 11,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,31; 207,02</t>
+          <t>2,44; 32,86</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,38</t>
+          <t>6,52</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>12,2</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,55</t>
+          <t>9,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 10,67</t>
+          <t>0,69; 10,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 8,37</t>
+          <t>-0,76; 8,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 13,46</t>
+          <t>1,83; 10,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,25; 13,95</t>
+          <t>5,47; 14,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 8,03</t>
+          <t>-0,73; 7,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,52; 15,26</t>
+          <t>7,9; 16,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,91; 11,67</t>
+          <t>4,57; 11,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 6,62</t>
+          <t>0,35; 6,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,81; 13,17</t>
+          <t>6,78; 12,93</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>68,49%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10,49; 109,52</t>
+          <t>4,36; 107,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 86,71</t>
+          <t>-5,4; 80,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19,44; 141,93</t>
+          <t>11,51; 112,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29,71; 106,23</t>
+          <t>29,56; 108,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 60,33</t>
+          <t>-4,28; 56,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,5; 112,83</t>
+          <t>43,02; 122,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,18; 92,38</t>
+          <t>27,54; 93,77</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,11; 53,36</t>
+          <t>2,17; 54,16</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>33,06; 103,25</t>
+          <t>41,06; 104,41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,71</t>
+          <t>3,69</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,32</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,93</t>
+          <t>-2,0; 2,32</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,82</t>
+          <t>-2,6; 0,85</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,25</t>
+          <t>-1,43; 2,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,95; 10,47</t>
+          <t>2,52; 10,1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 6,38</t>
+          <t>-1,25; 6,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,13; 8,47</t>
+          <t>-0,26; 7,27</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,9; 8,44</t>
+          <t>1,94; 8,32</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 4,58</t>
+          <t>-1,6; 4,61</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 5,61</t>
+          <t>-0,71; 5,47</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-83,93; 271,66</t>
+          <t>-82,35; 471,77</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 297,54</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-70,69; 424,06</t>
+          <t>-64,92; 476,44</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10,72; 44,92</t>
+          <t>9,66; 44,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 27,43</t>
+          <t>-4,79; 27,57</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,27; 36,17</t>
+          <t>-1,05; 31,38</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,56; 44,06</t>
+          <t>8,98; 44,27</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 23,98</t>
+          <t>-7,65; 23,88</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 28,7</t>
+          <t>-3,46; 28,86</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>6,32</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,57</t>
+          <t>4,29</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>5,3</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,6</t>
+          <t>2,1; 5,52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,79</t>
+          <t>0,38; 3,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,39</t>
+          <t>4,59; 8,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,01</t>
+          <t>2,14; 6,11</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,66</t>
+          <t>-0,96; 2,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,34; 23,55</t>
+          <t>2,44; 5,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,17</t>
+          <t>2,6; 5,32</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,68</t>
+          <t>0,18; 2,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,84; 16,64</t>
+          <t>4,12; 6,58</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>14,88; 45,28</t>
+          <t>14,99; 45,2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3,54; 31,16</t>
+          <t>2,67; 30,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8,16; 58,39</t>
+          <t>33,22; 65,63</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10,71; 37,27</t>
+          <t>11,93; 38,04</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 16,93</t>
+          <t>-5,46; 17,63</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,63; 142,76</t>
+          <t>13,47; 36,93</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,68; 35,87</t>
+          <t>16,58; 36,96</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,94; 18,56</t>
+          <t>1,16; 17,98</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25,1; 114,57</t>
+          <t>26,37; 46,19</t>
         </is>
       </c>
     </row>
